--- a/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Univariado/Fichas/estadisticas_univariadas.xlsx
+++ b/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Univariado/Fichas/estadisticas_univariadas.xlsx
@@ -1042,34 +1042,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>528</v>
+        <v>336</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>63.64</v>
       </c>
       <c r="G12" t="n">
-        <v>0.083</v>
+        <v>437503454.92</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>432174766.337</v>
       </c>
       <c r="I12" t="n">
-        <v>0.277</v>
+        <v>93579100.669</v>
       </c>
       <c r="J12" t="n">
-        <v>331.98</v>
+        <v>21.39</v>
       </c>
       <c r="K12" t="n">
-        <v>3.024</v>
+        <v>0.124</v>
       </c>
       <c r="L12" t="n">
-        <v>7.17</v>
+        <v>-1.093</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1100,28 +1100,28 @@
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0.091</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.288</v>
+        <v>2.412</v>
       </c>
       <c r="J13" t="n">
-        <v>316.53</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>2.854</v>
+        <v>1.018</v>
       </c>
       <c r="L13" t="n">
-        <v>6.17</v>
+        <v>0.361</v>
       </c>
       <c r="M13" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
-        <v>9.09</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="14">
@@ -1152,26 +1152,28 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>61680.568</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>37972.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>53355.792</v>
+      </c>
+      <c r="J14" t="n">
+        <v>86.5</v>
+      </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1.066</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.703</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1204,22 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.636</v>
+        <v>744.905</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>447.33</v>
       </c>
       <c r="I15" t="n">
-        <v>0.482</v>
+        <v>756.035</v>
       </c>
       <c r="J15" t="n">
-        <v>75.66</v>
+        <v>101.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.569</v>
+        <v>0.944</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.683</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1286,17 +1288,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>No definido</t>
+          <t>No documentado en C09/C10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No definida</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1306,28 +1308,28 @@
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>0.636</v>
+        <v>97.76900000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>0.482</v>
+        <v>4.345</v>
       </c>
       <c r="J17" t="n">
-        <v>75.66</v>
+        <v>4.44</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.569</v>
+        <v>-1.474</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.683</v>
+        <v>0.186</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="18">
@@ -1338,17 +1340,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>No definido</t>
+          <t>No documentado en C09/C10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No definida</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1358,28 +1360,28 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.636</v>
+        <v>93.178</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="I18" t="n">
-        <v>0.482</v>
+        <v>14.773</v>
       </c>
       <c r="J18" t="n">
-        <v>75.66</v>
+        <v>15.85</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.569</v>
+        <v>-3.296</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.683</v>
+        <v>10.609</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="19">
@@ -1410,28 +1412,28 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.636</v>
+        <v>99.818</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>0.482</v>
+        <v>0.386</v>
       </c>
       <c r="J19" t="n">
-        <v>75.66</v>
+        <v>0.39</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.569</v>
+        <v>-1.655</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.683</v>
+        <v>0.741</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="20">
@@ -1462,28 +1464,28 @@
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>0.636</v>
+        <v>95.318</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>0.482</v>
+        <v>7.706</v>
       </c>
       <c r="J20" t="n">
-        <v>75.66</v>
+        <v>8.08</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.569</v>
+        <v>-1.15</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.683</v>
+        <v>-0.668</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -1514,28 +1516,28 @@
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>0.636</v>
+        <v>87.68300000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>84.31</v>
       </c>
       <c r="I21" t="n">
-        <v>0.482</v>
+        <v>9.051</v>
       </c>
       <c r="J21" t="n">
-        <v>75.66</v>
+        <v>10.32</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.569</v>
+        <v>-0.161</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.683</v>
+        <v>-0.032</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="22">
@@ -1566,22 +1568,22 @@
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>0.636</v>
+        <v>45.103</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>55.88</v>
       </c>
       <c r="I22" t="n">
-        <v>0.482</v>
+        <v>26.898</v>
       </c>
       <c r="J22" t="n">
-        <v>75.66</v>
+        <v>59.64</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.569</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.683</v>
+        <v>-1.061</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
